--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486735_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486735_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.8687</v>
+        <v>9.7776</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9295</v>
+        <v>6.1363</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9392</v>
+        <v>3.6413</v>
       </c>
       <c r="G2" t="n">
         <v>8.835699999999999</v>
@@ -610,13 +610,13 @@
         <v>2.7031</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5464</v>
+        <v>0.4552</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.497</v>
+        <v>-0.2902</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0434</v>
+        <v>0.7454</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2856</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5252</v>
+        <v>5.7707</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4122</v>
+        <v>2.1362</v>
       </c>
       <c r="F3" t="n">
-        <v>3.113</v>
+        <v>3.6345</v>
       </c>
       <c r="G3" t="n">
         <v>4.8425</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2247</v>
+        <v>0.0207</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0209</v>
+        <v>-0.297</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2038</v>
+        <v>0.3177</v>
       </c>
       <c r="V3" t="n">
         <v>0.3282</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5213</v>
+        <v>4.8771</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3615</v>
+        <v>4.5683</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1598</v>
+        <v>0.3088</v>
       </c>
       <c r="G4" t="n">
         <v>3.1574</v>
@@ -766,13 +766,13 @@
         <v>2.7031</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3972</v>
+        <v>-0.0414</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.497</v>
+        <v>-0.2902</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0998</v>
+        <v>0.2488</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9421</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5745</v>
+        <v>2.8628</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9451</v>
+        <v>4.5314</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3706</v>
+        <v>-1.6686</v>
       </c>
       <c r="G5" t="n">
         <v>3.5628</v>
@@ -844,13 +844,13 @@
         <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4012</v>
+        <v>0.6895</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6339</v>
+        <v>0.2203</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7672</v>
+        <v>0.4692</v>
       </c>
       <c r="V5" t="n">
         <v>-2.741</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9012</v>
+        <v>2.439</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3526</v>
+        <v>1.7663</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5486</v>
+        <v>0.6727</v>
       </c>
       <c r="G6" t="n">
         <v>1.1387</v>
@@ -922,13 +922,13 @@
         <v>1.1585</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1104</v>
+        <v>0.4274</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0553</v>
+        <v>0.3584</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0551</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2856</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1465</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4717</v>
+        <v>-3.2991</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6182</v>
+        <v>3.2209</v>
       </c>
       <c r="G7" t="n">
         <v>-0.07820000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>2.3169</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8039</v>
+        <v>0.5792</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1027</v>
+        <v>0.2753</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7012</v>
+        <v>0.3039</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. RYTZ</t>
+          <t>E. QUIJADA GARCÍA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9845</v>
+        <v>-1.4964</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0272</v>
+        <v>-1.5308</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0426</v>
+        <v>0.0344</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9923</v>
+        <v>-1.5584</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7513</v>
+        <v>-0.5999</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2411</v>
+        <v>-0.9585</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.406</v>
+        <v>-1.3583</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.0271</v>
+        <v>-0.6688</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.379</v>
+        <v>-0.6895</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4137</v>
+        <v>-0.2002</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2758</v>
+        <v>0.0689</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1379</v>
+        <v>-0.269</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6216</v>
+        <v>0.062</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3788</v>
+        <v>-0.1725</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2428</v>
+        <v>0.2345</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. QUIJADA GARCÍA</t>
+          <t>M. MELERO JAREÑO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.575</v>
+        <v>-1.7182</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6342</v>
+        <v>-0.032</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0592</v>
+        <v>-1.6862</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5584</v>
+        <v>-0.0804</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5999</v>
+        <v>0.4622</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9585</v>
+        <v>-0.5425</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3583</v>
+        <v>-0.3628</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6688</v>
+        <v>0.3244</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6895</v>
+        <v>-0.6872</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2002</v>
+        <v>0.2824</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0689</v>
+        <v>0.1377</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.269</v>
+        <v>0.1447</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0166</v>
+        <v>0.5239</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2759</v>
+        <v>0.3307</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2594</v>
+        <v>0.1932</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.741</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MELERO JAREÑO</t>
+          <t>K. RYTZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9168</v>
+        <v>-1.7581</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.032</v>
+        <v>-2.7511</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8848</v>
+        <v>0.993</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0804</v>
+        <v>-2.9923</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4622</v>
+        <v>-1.7513</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5425</v>
+        <v>-1.2411</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3628</v>
+        <v>-3.406</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3244</v>
+        <v>-2.0271</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6872</v>
+        <v>-1.379</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2824</v>
+        <v>0.4137</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1377</v>
+        <v>0.2758</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1447</v>
+        <v>0.1379</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3253</v>
+        <v>0.848</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3307</v>
+        <v>0.6549</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0055</v>
+        <v>0.1931</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.741</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6024</v>
+        <v>-3.2177</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.6027</v>
+        <v>-5.2925</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0003</v>
+        <v>2.0748</v>
       </c>
       <c r="G11" t="n">
         <v>0.1401</v>
@@ -1312,13 +1312,13 @@
         <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9156</v>
+        <v>-0.5308</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8277</v>
+        <v>-0.5175</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.0134</v>
       </c>
       <c r="V11" t="n">
         <v>1.2277</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>17.4587</v>
+        <v>17.4586</v>
       </c>
       <c r="E12" t="n">
-        <v>6.233099999999999</v>
+        <v>6.232999999999997</v>
       </c>
       <c r="F12" t="n">
-        <v>11.2255</v>
+        <v>11.2256</v>
       </c>
       <c r="G12" t="n">
         <v>16.9679</v>
@@ -1360,7 +1360,7 @@
         <v>7.5858</v>
       </c>
       <c r="I12" t="n">
-        <v>9.382099999999999</v>
+        <v>9.382100000000001</v>
       </c>
       <c r="J12" t="n">
         <v>16.1831</v>
@@ -1369,7 +1369,7 @@
         <v>7.591999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>8.590999999999999</v>
+        <v>8.591000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>0.7847</v>
@@ -1381,7 +1381,7 @@
         <v>0.7908999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>2.896200000000001</v>
+        <v>2.8962</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.5501</v>
@@ -1390,13 +1390,13 @@
         <v>15.4462</v>
       </c>
       <c r="S12" t="n">
-        <v>3.0339</v>
+        <v>3.0337</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2723000000000001</v>
+        <v>0.2722</v>
       </c>
       <c r="U12" t="n">
-        <v>2.7615</v>
+        <v>2.7614</v>
       </c>
       <c r="V12" t="n">
         <v>-5.439400000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9106</v>
+        <v>4.7231</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2332</v>
+        <v>5.8195</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3226</v>
+        <v>-1.0965</v>
       </c>
       <c r="G13" t="n">
         <v>-0.1602</v>
@@ -1468,13 +1468,13 @@
         <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.033</v>
+        <v>-0.2206</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1375</v>
+        <v>-0.2761</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1705</v>
+        <v>0.0556</v>
       </c>
       <c r="V13" t="n">
         <v>4.9108</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8635</v>
+        <v>1.2538</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2476</v>
+        <v>0.351</v>
       </c>
       <c r="F14" t="n">
-        <v>0.616</v>
+        <v>0.9028</v>
       </c>
       <c r="G14" t="n">
         <v>0.9021</v>
@@ -1546,13 +1546,13 @@
         <v>0.7723</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8109</v>
+        <v>-0.4206</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4966</v>
+        <v>-0.3932</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3142</v>
+        <v>-0.0274</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2913</v>
+        <v>-0.0789</v>
       </c>
       <c r="E15" t="n">
         <v>-0.1104</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1809</v>
+        <v>0.0315</v>
       </c>
       <c r="G15" t="n">
         <v>0.2756</v>
@@ -1624,13 +1624,13 @@
         <v>0.1931</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4744</v>
+        <v>-0.262</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.364</v>
+        <v>-0.1516</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2856</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>A. ALONSO LANTIGUA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.537</v>
+        <v>-2.098</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4016</v>
+        <v>-3.1319</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1354</v>
+        <v>1.034</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9466</v>
+        <v>-1.8552</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0476</v>
+        <v>-1.0414</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.899</v>
+        <v>-0.8138</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4346</v>
+        <v>-2.0064</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4707</v>
+        <v>-1.3169</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0361</v>
+        <v>-0.6895</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.3811</v>
+        <v>0.1511</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5183</v>
+        <v>0.2755</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8629</v>
+        <v>-0.1244</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0892</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3169</v>
+        <v>0.9654</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2244</v>
+        <v>-0.5516</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2957</v>
+        <v>-0.4691</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0712</v>
+        <v>-0.0825</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0426</v>
+        <v>-0.6565</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0426</v>
+        <v>-0.6565</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ALONSO LANTIGUA</t>
+          <t>A. CHACON GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.3241</v>
+        <v>-2.1395</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.1319</v>
+        <v>-2.3798</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8078</v>
+        <v>0.2403</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8552</v>
+        <v>-2.6635</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0414</v>
+        <v>-2.1864</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8138</v>
+        <v>-0.4771</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.0064</v>
+        <v>-1.1107</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3169</v>
+        <v>-1.1513</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6895</v>
+        <v>0.0407</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1511</v>
+        <v>-1.5528</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2755</v>
+        <v>-1.0351</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1244</v>
+        <v>-0.5178</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9654</v>
+        <v>1.5446</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7778</v>
+        <v>0.1378</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4691</v>
+        <v>-0.1107</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3087</v>
+        <v>0.2486</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CHACON GARCIA</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8401</v>
+        <v>-2.4375</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.7935</v>
+        <v>-1.5393</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0465</v>
+        <v>-0.8982</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6635</v>
+        <v>-1.9466</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1864</v>
+        <v>-0.0476</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4771</v>
+        <v>-1.899</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1107</v>
+        <v>1.4346</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1513</v>
+        <v>1.4707</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0407</v>
+        <v>-0.0361</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5528</v>
+        <v>-3.3811</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0351</v>
+        <v>-1.5183</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5178</v>
+        <v>-1.8629</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3862</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1585</v>
+        <v>-3.0892</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5446</v>
+        <v>2.3169</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5627</v>
+        <v>0.324</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5244</v>
+        <v>0.158</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0383</v>
+        <v>0.166</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.0426</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.0426</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0208</v>
+        <v>-2.6719</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1366</v>
+        <v>0.4469</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1574</v>
+        <v>-3.1188</v>
       </c>
       <c r="G19" t="n">
         <v>-2.8578</v>
@@ -1936,13 +1936,13 @@
         <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.673</v>
+        <v>-0.3242</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8832</v>
+        <v>-0.5729</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2102</v>
+        <v>0.2487</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2277</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3274</v>
+        <v>-3.9041</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0075</v>
+        <v>-3.6973</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3199</v>
+        <v>-0.2068</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8604</v>
@@ -2014,13 +2014,13 @@
         <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8991</v>
+        <v>-0.4758</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.883</v>
+        <v>-0.5728</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0161</v>
+        <v>0.097</v>
       </c>
       <c r="V20" t="n">
         <v>0.9421</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.891999999999999</v>
+        <v>-8.726699999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.398</v>
+        <v>-6.9843</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4941</v>
+        <v>-1.7424</v>
       </c>
       <c r="G21" t="n">
         <v>-6.802</v>
@@ -2092,13 +2092,13 @@
         <v>2.1239</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0274</v>
+        <v>0.138</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.828</v>
+        <v>-0.4143</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8006</v>
+        <v>0.5522</v>
       </c>
       <c r="V21" t="n">
         <v>1.7989</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-17.4586</v>
+        <v>-16.0797</v>
       </c>
       <c r="E22" t="n">
-        <v>-11.2255</v>
+        <v>-11.2256</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.233000000000001</v>
+        <v>-4.854099999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-16.968</v>
@@ -2140,7 +2140,7 @@
         <v>-7.585900000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-9.382099999999999</v>
+        <v>-9.382100000000001</v>
       </c>
       <c r="J22" t="n">
         <v>-0.7848999999999999</v>
@@ -2155,7 +2155,7 @@
         <v>-16.1832</v>
       </c>
       <c r="N22" t="n">
-        <v>-7.592099999999999</v>
+        <v>-7.5921</v>
       </c>
       <c r="O22" t="n">
         <v>-8.591200000000001</v>
@@ -2170,13 +2170,13 @@
         <v>12.5501</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.0339</v>
+        <v>-1.655</v>
       </c>
       <c r="T22" t="n">
         <v>-2.7615</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2722</v>
+        <v>1.1066</v>
       </c>
       <c r="V22" t="n">
         <v>5.4394</v>
